--- a/output/pdf_financials_xlsx/NVRS.xlsx
+++ b/output/pdf_financials_xlsx/NVRS.xlsx
@@ -2365,7 +2365,7 @@
         <v>-3.174901</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>2.921153</v>
+        <v>-2.921153</v>
       </c>
     </row>
     <row r="100">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>3.403114</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>1.879987</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.019278</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>4.619393</v>
+        <v>8.022506999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>3.29644</v>
+        <v>5.176427</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>2.173457</v>
+        <v>2.192735</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.443667</v>
@@ -3896,7 +3896,11 @@
           <t>Prepaids and deposits 5</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -4372,7 +4376,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>1.220349</v>
       </c>
@@ -4444,7 +4452,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.678916</v>
       </c>
@@ -5083,7 +5095,7 @@
         <v>-3.174901</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>2.921153</v>
+        <v>-2.921153</v>
       </c>
     </row>
     <row r="56">
@@ -5422,7 +5434,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6266,7 +6282,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7402,7 +7422,11 @@
           <t>Prepaids and deposits 1,879,987</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>3.403114</v>
       </c>

--- a/output/pdf_financials_xlsx/NVRS.xlsx
+++ b/output/pdf_financials_xlsx/NVRS.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10.556197</v>
+        <v>17.058264</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6.539527</v>
+        <v>10.852691</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.092151</v>
+        <v>4.321621</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.556407</v>
+        <v>0.548714</v>
       </c>
     </row>
     <row r="11">
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-6.539527</v>
+        <v>-10.852691</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.092151</v>
+        <v>-4.321621</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.556407</v>
+        <v>-0.548714</v>
       </c>
     </row>
     <row r="12">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.01103</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.037646</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000325</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009698999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.01103</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.037646</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000325</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009698999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.181398</v>
+        <v>8.170368</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.056924</v>
+        <v>0.019278</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.035466</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.035466</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -7648,7 +7648,11 @@
           <t>Lease payments -</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>-0.035466</v>
       </c>
@@ -8524,7 +8528,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8536,10 +8540,10 @@
         <v>10.852691</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>-4.321621</v>
+        <v>4.321621</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>-0.548714</v>
+        <v>0.548714</v>
       </c>
     </row>
     <row r="150">
@@ -10714,7 +10718,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E209" s="5" t="n">

--- a/output/pdf_financials_xlsx/NVRS.xlsx
+++ b/output/pdf_financials_xlsx/NVRS.xlsx
@@ -9210,7 +9210,11 @@
           <t>Depreciation – property and equipment</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -10328,7 +10332,11 @@
           <t>Depreciation – property and equipment 7 9,876</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n">
         <v>0.128861</v>
       </c>

--- a/output/pdf_financials_xlsx/NVRS.xlsx
+++ b/output/pdf_financials_xlsx/NVRS.xlsx
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>3.827766</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>4.157459</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.783646</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.919992</v>
       </c>
     </row>
     <row r="65">
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.210832</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.193367</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.324894</v>
       </c>
     </row>
     <row r="68">
